--- a/OrganizedData/2026_organized/SpecimenDimensions2026.xlsx
+++ b/OrganizedData/2026_organized/SpecimenDimensions2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A849BE-6A10-4622-9F54-798DBEF13786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53130088-4AB1-499E-BC5A-22D76DF998BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="batch1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="16">
   <si>
     <t>Section</t>
   </si>
@@ -443,13 +443,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K169"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K211"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10453</v>
       </c>
@@ -497,8 +497,14 @@
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <v>24.78</v>
+      </c>
+      <c r="J2">
+        <v>12.58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10453</v>
       </c>
@@ -511,8 +517,14 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="I3">
+        <v>25.39</v>
+      </c>
+      <c r="J3">
+        <v>12.92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>10453</v>
       </c>
@@ -525,8 +537,20 @@
       <c r="D4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>25.4</v>
+      </c>
+      <c r="F4">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="G4">
+        <v>14.25</v>
+      </c>
+      <c r="H4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>10453</v>
       </c>
@@ -539,8 +563,20 @@
       <c r="D5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>25.4</v>
+      </c>
+      <c r="F5">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="G5">
+        <v>14.25</v>
+      </c>
+      <c r="H5">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>10453</v>
       </c>
@@ -553,8 +589,20 @@
       <c r="D6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>25.4</v>
+      </c>
+      <c r="F6">
+        <v>9.26</v>
+      </c>
+      <c r="G6">
+        <v>14.25</v>
+      </c>
+      <c r="H6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>10453</v>
       </c>
@@ -567,8 +615,20 @@
       <c r="D7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>25.4</v>
+      </c>
+      <c r="F7">
+        <v>9.84</v>
+      </c>
+      <c r="G7">
+        <v>14.25</v>
+      </c>
+      <c r="H7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>10453</v>
       </c>
@@ -581,8 +641,20 @@
       <c r="D8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>25.4</v>
+      </c>
+      <c r="F8">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="G8">
+        <v>14.25</v>
+      </c>
+      <c r="H8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>10453</v>
       </c>
@@ -595,8 +667,20 @@
       <c r="D9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>25.4</v>
+      </c>
+      <c r="F9">
+        <v>9.18</v>
+      </c>
+      <c r="G9">
+        <v>14.25</v>
+      </c>
+      <c r="H9">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10453</v>
       </c>
@@ -609,8 +693,20 @@
       <c r="D10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>25.4</v>
+      </c>
+      <c r="F10">
+        <v>10.72</v>
+      </c>
+      <c r="G10">
+        <v>14.25</v>
+      </c>
+      <c r="H10">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10453</v>
       </c>
@@ -623,8 +719,20 @@
       <c r="D11">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <v>25.4</v>
+      </c>
+      <c r="F11">
+        <v>10.74</v>
+      </c>
+      <c r="G11">
+        <v>14.25</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10453</v>
       </c>
@@ -637,8 +745,17 @@
       <c r="D12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E12">
+        <v>12.18</v>
+      </c>
+      <c r="F12">
+        <v>5.95</v>
+      </c>
+      <c r="K12">
+        <v>67.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10453</v>
       </c>
@@ -651,8 +768,17 @@
       <c r="D13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E13">
+        <v>13.47</v>
+      </c>
+      <c r="F13">
+        <v>5.98</v>
+      </c>
+      <c r="K13">
+        <v>72.41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>10457</v>
       </c>
@@ -665,8 +791,14 @@
       <c r="D14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <v>25.3</v>
+      </c>
+      <c r="J14">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>10457</v>
       </c>
@@ -679,8 +811,14 @@
       <c r="D15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <v>25.92</v>
+      </c>
+      <c r="J15">
+        <v>13.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>10457</v>
       </c>
@@ -693,8 +831,20 @@
       <c r="D16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E16">
+        <v>25.4</v>
+      </c>
+      <c r="F16">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G16">
+        <v>14.25</v>
+      </c>
+      <c r="H16">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>10457</v>
       </c>
@@ -707,8 +857,20 @@
       <c r="D17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E17">
+        <v>25.4</v>
+      </c>
+      <c r="F17">
+        <v>10.39</v>
+      </c>
+      <c r="G17">
+        <v>14.25</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>10457</v>
       </c>
@@ -721,8 +883,20 @@
       <c r="D18">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E18">
+        <v>25.4</v>
+      </c>
+      <c r="F18">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="G18">
+        <v>14.25</v>
+      </c>
+      <c r="H18">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>10457</v>
       </c>
@@ -735,8 +909,20 @@
       <c r="D19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E19">
+        <v>25.4</v>
+      </c>
+      <c r="F19">
+        <v>8.31</v>
+      </c>
+      <c r="G19">
+        <v>14.25</v>
+      </c>
+      <c r="H19">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>10457</v>
       </c>
@@ -749,8 +935,20 @@
       <c r="D20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E20">
+        <v>25.4</v>
+      </c>
+      <c r="F20">
+        <v>10.47</v>
+      </c>
+      <c r="G20">
+        <v>14.25</v>
+      </c>
+      <c r="H20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>10457</v>
       </c>
@@ -763,8 +961,20 @@
       <c r="D21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E21">
+        <v>25.4</v>
+      </c>
+      <c r="F21">
+        <v>9.68</v>
+      </c>
+      <c r="G21">
+        <v>14.25</v>
+      </c>
+      <c r="H21">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>10457</v>
       </c>
@@ -777,8 +987,20 @@
       <c r="D22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E22">
+        <v>25.4</v>
+      </c>
+      <c r="F22">
+        <v>9.99</v>
+      </c>
+      <c r="G22">
+        <v>14.25</v>
+      </c>
+      <c r="H22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>10457</v>
       </c>
@@ -791,36 +1013,60 @@
       <c r="D23">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E23">
+        <v>25.4</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>14.25</v>
+      </c>
+      <c r="H23">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>10457</v>
+        <v>10449</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <v>25.24</v>
+      </c>
+      <c r="J24">
+        <v>13.01</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>10457</v>
+        <v>10449</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <v>25.63</v>
+      </c>
+      <c r="J25">
+        <v>12.87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>10449</v>
       </c>
@@ -828,27 +1074,51 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E26">
+        <v>25.4</v>
+      </c>
+      <c r="F26">
+        <v>10.15</v>
+      </c>
+      <c r="G26">
+        <v>14.25</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>10449</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>25.4</v>
+      </c>
+      <c r="F27">
+        <v>10.47</v>
+      </c>
+      <c r="G27">
+        <v>14.25</v>
+      </c>
+      <c r="H27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>10449</v>
       </c>
@@ -859,10 +1129,22 @@
         <v>14</v>
       </c>
       <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>25.4</v>
+      </c>
+      <c r="F28">
+        <v>9.66</v>
+      </c>
+      <c r="G28">
+        <v>14.25</v>
+      </c>
+      <c r="H28">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>10449</v>
       </c>
@@ -873,38 +1155,74 @@
         <v>14</v>
       </c>
       <c r="D29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>25.4</v>
+      </c>
+      <c r="F29">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="G29">
+        <v>14.25</v>
+      </c>
+      <c r="H29">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>10449</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>25.4</v>
+      </c>
+      <c r="F30">
+        <v>10.54</v>
+      </c>
+      <c r="G30">
+        <v>14.25</v>
+      </c>
+      <c r="H30">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>10449</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
       </c>
       <c r="D31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>25.4</v>
+      </c>
+      <c r="F31">
+        <v>9.92</v>
+      </c>
+      <c r="G31">
+        <v>14.25</v>
+      </c>
+      <c r="H31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>10449</v>
       </c>
@@ -915,10 +1233,22 @@
         <v>14</v>
       </c>
       <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>25.4</v>
+      </c>
+      <c r="F32">
+        <v>11.16</v>
+      </c>
+      <c r="G32">
+        <v>14.25</v>
+      </c>
+      <c r="H32">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>10449</v>
       </c>
@@ -929,24 +1259,45 @@
         <v>14</v>
       </c>
       <c r="D33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>25.4</v>
+      </c>
+      <c r="F33">
+        <v>10.28</v>
+      </c>
+      <c r="G33">
+        <v>14.25</v>
+      </c>
+      <c r="H33">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>10449</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>13.28</v>
+      </c>
+      <c r="F34">
+        <v>5.92</v>
+      </c>
+      <c r="K34">
+        <v>65.56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>10449</v>
       </c>
@@ -954,41 +1305,62 @@
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>14.52</v>
+      </c>
+      <c r="F35">
+        <v>7.34</v>
+      </c>
+      <c r="K35">
+        <v>60.54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>10449</v>
+        <v>10440</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <v>25.06</v>
+      </c>
+      <c r="J36">
+        <v>12.72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>10449</v>
+        <v>10440</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <v>25.33</v>
+      </c>
+      <c r="J37">
+        <v>13.03</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>10440</v>
       </c>
@@ -996,27 +1368,51 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E38">
+        <v>25.4</v>
+      </c>
+      <c r="F38">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="G38">
+        <v>14.25</v>
+      </c>
+      <c r="H38">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>10440</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>25.4</v>
+      </c>
+      <c r="F39">
+        <v>10.07</v>
+      </c>
+      <c r="G39">
+        <v>14.25</v>
+      </c>
+      <c r="H39">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>10440</v>
       </c>
@@ -1027,10 +1423,22 @@
         <v>14</v>
       </c>
       <c r="D40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>25.4</v>
+      </c>
+      <c r="F40">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="G40">
+        <v>14.25</v>
+      </c>
+      <c r="H40">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>10440</v>
       </c>
@@ -1041,38 +1449,74 @@
         <v>14</v>
       </c>
       <c r="D41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>25.4</v>
+      </c>
+      <c r="F41">
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="G41">
+        <v>14.25</v>
+      </c>
+      <c r="H41">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>10440</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
       </c>
       <c r="D42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>25.4</v>
+      </c>
+      <c r="F42">
+        <v>10.47</v>
+      </c>
+      <c r="G42">
+        <v>14.25</v>
+      </c>
+      <c r="H42">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>10440</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
       </c>
       <c r="D43">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E43">
+        <v>25.4</v>
+      </c>
+      <c r="F43">
+        <v>9.49</v>
+      </c>
+      <c r="G43">
+        <v>14.25</v>
+      </c>
+      <c r="H43">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>10440</v>
       </c>
@@ -1083,10 +1527,22 @@
         <v>14</v>
       </c>
       <c r="D44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E44">
+        <v>25.4</v>
+      </c>
+      <c r="F44">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="G44">
+        <v>14.25</v>
+      </c>
+      <c r="H44">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>10440</v>
       </c>
@@ -1097,24 +1553,45 @@
         <v>14</v>
       </c>
       <c r="D45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E45">
+        <v>25.4</v>
+      </c>
+      <c r="F45">
+        <v>9.34</v>
+      </c>
+      <c r="G45">
+        <v>14.25</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>10440</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D46">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>13.21</v>
+      </c>
+      <c r="F46">
+        <v>6.06</v>
+      </c>
+      <c r="K46">
+        <v>67.14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>10440</v>
       </c>
@@ -1122,41 +1599,62 @@
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D47">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>13.08</v>
+      </c>
+      <c r="F47">
+        <v>6.39</v>
+      </c>
+      <c r="K47">
+        <v>65.930000000000007</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>10440</v>
+        <v>10443</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <v>25.7</v>
+      </c>
+      <c r="J48">
+        <v>13.03</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>10440</v>
+        <v>10443</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <v>26.26</v>
+      </c>
+      <c r="J49">
+        <v>12.83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>10443</v>
       </c>
@@ -1164,27 +1662,51 @@
         <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E50">
+        <v>25.4</v>
+      </c>
+      <c r="F50">
+        <v>10.25</v>
+      </c>
+      <c r="G50">
+        <v>14.25</v>
+      </c>
+      <c r="H50">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>10443</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E51">
+        <v>25.4</v>
+      </c>
+      <c r="F51">
+        <v>10.17</v>
+      </c>
+      <c r="G51">
+        <v>14.25</v>
+      </c>
+      <c r="H51">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>10443</v>
       </c>
@@ -1195,10 +1717,22 @@
         <v>14</v>
       </c>
       <c r="D52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>25.4</v>
+      </c>
+      <c r="F52">
+        <v>8.36</v>
+      </c>
+      <c r="G52">
+        <v>14.25</v>
+      </c>
+      <c r="H52">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>10443</v>
       </c>
@@ -1209,38 +1743,74 @@
         <v>14</v>
       </c>
       <c r="D53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E53">
+        <v>25.4</v>
+      </c>
+      <c r="F53">
+        <v>9.35</v>
+      </c>
+      <c r="G53">
+        <v>14.25</v>
+      </c>
+      <c r="H53">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>10443</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>25.4</v>
+      </c>
+      <c r="F54">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="G54">
+        <v>14.25</v>
+      </c>
+      <c r="H54">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>10443</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E55">
+        <v>25.4</v>
+      </c>
+      <c r="F55">
+        <v>10.14</v>
+      </c>
+      <c r="G55">
+        <v>14.25</v>
+      </c>
+      <c r="H55">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>10443</v>
       </c>
@@ -1251,10 +1821,22 @@
         <v>14</v>
       </c>
       <c r="D56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E56">
+        <v>25.4</v>
+      </c>
+      <c r="F56">
+        <v>10.38</v>
+      </c>
+      <c r="G56">
+        <v>14.25</v>
+      </c>
+      <c r="H56">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>10443</v>
       </c>
@@ -1265,24 +1847,45 @@
         <v>14</v>
       </c>
       <c r="D57">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E57">
+        <v>25.4</v>
+      </c>
+      <c r="F57">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="G57">
+        <v>14.25</v>
+      </c>
+      <c r="H57">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>10443</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D58">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>13.76</v>
+      </c>
+      <c r="F58">
+        <v>6.32</v>
+      </c>
+      <c r="K58">
+        <v>66.260000000000005</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>10443</v>
       </c>
@@ -1290,41 +1893,62 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D59">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>14.51</v>
+      </c>
+      <c r="F59">
+        <v>7.95</v>
+      </c>
+      <c r="K59">
+        <v>66.260000000000005</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>10443</v>
+        <v>10442</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <v>24.86</v>
+      </c>
+      <c r="J60">
+        <v>12.88</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>10443</v>
+        <v>10442</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <v>24.66</v>
+      </c>
+      <c r="J61">
+        <v>13.02</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>10442</v>
       </c>
@@ -1332,27 +1956,51 @@
         <v>11</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E62">
+        <v>25.4</v>
+      </c>
+      <c r="F62">
+        <v>9.48</v>
+      </c>
+      <c r="G62">
+        <v>14.25</v>
+      </c>
+      <c r="H62">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>10442</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E63">
+        <v>25.4</v>
+      </c>
+      <c r="F63">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="G63">
+        <v>14.25</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>10442</v>
       </c>
@@ -1363,10 +2011,22 @@
         <v>14</v>
       </c>
       <c r="D64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E64">
+        <v>25.4</v>
+      </c>
+      <c r="F64">
+        <v>10.37</v>
+      </c>
+      <c r="G64">
+        <v>14.25</v>
+      </c>
+      <c r="H64">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>10442</v>
       </c>
@@ -1377,38 +2037,74 @@
         <v>14</v>
       </c>
       <c r="D65">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E65">
+        <v>25.4</v>
+      </c>
+      <c r="F65">
+        <v>8.9</v>
+      </c>
+      <c r="G65">
+        <v>14.25</v>
+      </c>
+      <c r="H65">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>10442</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
       </c>
       <c r="D66">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>25.4</v>
+      </c>
+      <c r="F66">
+        <v>10.69</v>
+      </c>
+      <c r="G66">
+        <v>14.25</v>
+      </c>
+      <c r="H66">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>10442</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E67">
+        <v>25.4</v>
+      </c>
+      <c r="F67">
+        <v>10.64</v>
+      </c>
+      <c r="G67">
+        <v>14.25</v>
+      </c>
+      <c r="H67">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>10442</v>
       </c>
@@ -1419,10 +2115,22 @@
         <v>14</v>
       </c>
       <c r="D68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E68">
+        <v>25.4</v>
+      </c>
+      <c r="F68">
+        <v>10.34</v>
+      </c>
+      <c r="G68">
+        <v>14.25</v>
+      </c>
+      <c r="H68">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>10442</v>
       </c>
@@ -1433,24 +2141,45 @@
         <v>14</v>
       </c>
       <c r="D69">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <v>25.4</v>
+      </c>
+      <c r="F69">
+        <v>10.1</v>
+      </c>
+      <c r="G69">
+        <v>14.25</v>
+      </c>
+      <c r="H69">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>10442</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D70">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>13.04</v>
+      </c>
+      <c r="F70">
+        <v>5.53</v>
+      </c>
+      <c r="K70">
+        <v>66.73</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>10442</v>
       </c>
@@ -1458,41 +2187,62 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D71">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>12.8</v>
+      </c>
+      <c r="F71">
+        <v>6.48</v>
+      </c>
+      <c r="K71">
+        <v>66.64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>10442</v>
+        <v>10447</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <v>25.51</v>
+      </c>
+      <c r="J72">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>10442</v>
+        <v>10447</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I73">
+        <v>25.5</v>
+      </c>
+      <c r="J73">
+        <v>13.09</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>10447</v>
       </c>
@@ -1500,27 +2250,51 @@
         <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E74">
+        <v>25.4</v>
+      </c>
+      <c r="F74">
+        <v>9.35</v>
+      </c>
+      <c r="G74">
+        <v>14.25</v>
+      </c>
+      <c r="H74">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>10447</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <v>25.4</v>
+      </c>
+      <c r="F75">
+        <v>9.26</v>
+      </c>
+      <c r="G75">
+        <v>14.25</v>
+      </c>
+      <c r="H75">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>10447</v>
       </c>
@@ -1531,10 +2305,22 @@
         <v>14</v>
       </c>
       <c r="D76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E76">
+        <v>25.4</v>
+      </c>
+      <c r="F76">
+        <v>9.64</v>
+      </c>
+      <c r="G76">
+        <v>14.25</v>
+      </c>
+      <c r="H76">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>10447</v>
       </c>
@@ -1545,38 +2331,74 @@
         <v>14</v>
       </c>
       <c r="D77">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E77">
+        <v>25.4</v>
+      </c>
+      <c r="F77">
+        <v>9.6</v>
+      </c>
+      <c r="G77">
+        <v>14.25</v>
+      </c>
+      <c r="H77">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>10447</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
       <c r="D78">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>25.4</v>
+      </c>
+      <c r="F78">
+        <v>11.25</v>
+      </c>
+      <c r="G78">
+        <v>14.25</v>
+      </c>
+      <c r="H78">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>10447</v>
       </c>
       <c r="B79" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E79">
+        <v>25.4</v>
+      </c>
+      <c r="F79">
+        <v>9.64</v>
+      </c>
+      <c r="G79">
+        <v>14.25</v>
+      </c>
+      <c r="H79">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>10447</v>
       </c>
@@ -1587,10 +2409,22 @@
         <v>14</v>
       </c>
       <c r="D80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E80">
+        <v>25.4</v>
+      </c>
+      <c r="F80">
+        <v>10.47</v>
+      </c>
+      <c r="G80">
+        <v>14.25</v>
+      </c>
+      <c r="H80">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>10447</v>
       </c>
@@ -1601,24 +2435,45 @@
         <v>14</v>
       </c>
       <c r="D81">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E81">
+        <v>25.4</v>
+      </c>
+      <c r="F81">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="G81">
+        <v>14.25</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>10447</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D82">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>13.42</v>
+      </c>
+      <c r="F82">
+        <v>5.68</v>
+      </c>
+      <c r="K82">
+        <v>66.87</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>10447</v>
       </c>
@@ -1626,41 +2481,62 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D83">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>13.75</v>
+      </c>
+      <c r="F83">
+        <v>6.34</v>
+      </c>
+      <c r="K83">
+        <v>66.180000000000007</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>10447</v>
+        <v>10450</v>
       </c>
       <c r="B84" t="s">
         <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I84">
+        <v>25.6</v>
+      </c>
+      <c r="J84">
+        <v>12.88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>10447</v>
+        <v>10450</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I85">
+        <v>25.56</v>
+      </c>
+      <c r="J85">
+        <v>13.09</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>10450</v>
       </c>
@@ -1668,27 +2544,51 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E86">
+        <v>25.4</v>
+      </c>
+      <c r="F86">
+        <v>9.66</v>
+      </c>
+      <c r="G86">
+        <v>14.25</v>
+      </c>
+      <c r="H86">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>10450</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E87">
+        <v>25.4</v>
+      </c>
+      <c r="F87">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="G87">
+        <v>14.25</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>10450</v>
       </c>
@@ -1699,10 +2599,22 @@
         <v>14</v>
       </c>
       <c r="D88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E88">
+        <v>25.4</v>
+      </c>
+      <c r="F88">
+        <v>9.65</v>
+      </c>
+      <c r="G88">
+        <v>14.25</v>
+      </c>
+      <c r="H88">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>10450</v>
       </c>
@@ -1713,38 +2625,74 @@
         <v>14</v>
       </c>
       <c r="D89">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E89">
+        <v>25.4</v>
+      </c>
+      <c r="F89">
+        <v>8.74</v>
+      </c>
+      <c r="G89">
+        <v>14.25</v>
+      </c>
+      <c r="H89">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>10450</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>25.4</v>
+      </c>
+      <c r="F90">
+        <v>10.51</v>
+      </c>
+      <c r="G90">
+        <v>14.25</v>
+      </c>
+      <c r="H90">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>10450</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
       </c>
       <c r="D91">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E91">
+        <v>25.4</v>
+      </c>
+      <c r="F91">
+        <v>9.41</v>
+      </c>
+      <c r="G91">
+        <v>14.25</v>
+      </c>
+      <c r="H91">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>10450</v>
       </c>
@@ -1755,10 +2703,22 @@
         <v>14</v>
       </c>
       <c r="D92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <v>25.4</v>
+      </c>
+      <c r="F92">
+        <v>10.36</v>
+      </c>
+      <c r="G92">
+        <v>14.25</v>
+      </c>
+      <c r="H92">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>10450</v>
       </c>
@@ -1769,24 +2729,45 @@
         <v>14</v>
       </c>
       <c r="D93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E93">
+        <v>25.4</v>
+      </c>
+      <c r="F93">
+        <v>9.89</v>
+      </c>
+      <c r="G93">
+        <v>14.25</v>
+      </c>
+      <c r="H93">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>10450</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D94">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>13.37</v>
+      </c>
+      <c r="F94">
+        <v>5.54</v>
+      </c>
+      <c r="K94">
+        <v>66.099999999999994</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>10450</v>
       </c>
@@ -1794,41 +2775,62 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D95">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>13.69</v>
+      </c>
+      <c r="F95">
+        <v>6.45</v>
+      </c>
+      <c r="K95">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>10450</v>
+        <v>10448</v>
       </c>
       <c r="B96" t="s">
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I96">
+        <v>25.79</v>
+      </c>
+      <c r="J96">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>10450</v>
+        <v>10448</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I97">
+        <v>26.35</v>
+      </c>
+      <c r="J97">
+        <v>12.62</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>10448</v>
       </c>
@@ -1836,27 +2838,51 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E98">
+        <v>25.4</v>
+      </c>
+      <c r="F98">
+        <v>9.61</v>
+      </c>
+      <c r="G98">
+        <v>14.25</v>
+      </c>
+      <c r="H98">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>10448</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E99">
+        <v>25.4</v>
+      </c>
+      <c r="F99">
+        <v>9.18</v>
+      </c>
+      <c r="G99">
+        <v>14.25</v>
+      </c>
+      <c r="H99">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>10448</v>
       </c>
@@ -1867,10 +2893,22 @@
         <v>14</v>
       </c>
       <c r="D100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E100">
+        <v>25.4</v>
+      </c>
+      <c r="F100">
+        <v>9.4</v>
+      </c>
+      <c r="G100">
+        <v>14.25</v>
+      </c>
+      <c r="H100">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>10448</v>
       </c>
@@ -1881,38 +2919,74 @@
         <v>14</v>
       </c>
       <c r="D101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E101">
+        <v>25.4</v>
+      </c>
+      <c r="F101">
+        <v>8.64</v>
+      </c>
+      <c r="G101">
+        <v>14.25</v>
+      </c>
+      <c r="H101">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>10448</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
       </c>
       <c r="D102">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>25.4</v>
+      </c>
+      <c r="F102">
+        <v>10.5</v>
+      </c>
+      <c r="G102">
+        <v>14.25</v>
+      </c>
+      <c r="H102">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>10448</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
       </c>
       <c r="D103">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E103">
+        <v>25.4</v>
+      </c>
+      <c r="F103">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="G103">
+        <v>14.25</v>
+      </c>
+      <c r="H103">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>10448</v>
       </c>
@@ -1923,10 +2997,22 @@
         <v>14</v>
       </c>
       <c r="D104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E104">
+        <v>25.4</v>
+      </c>
+      <c r="F104">
+        <v>9.69</v>
+      </c>
+      <c r="G104">
+        <v>14.25</v>
+      </c>
+      <c r="H104">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>10448</v>
       </c>
@@ -1937,24 +3023,45 @@
         <v>14</v>
       </c>
       <c r="D105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E105">
+        <v>25.4</v>
+      </c>
+      <c r="F105">
+        <v>10.71</v>
+      </c>
+      <c r="G105">
+        <v>14.25</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>10448</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C106" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D106">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>12.69</v>
+      </c>
+      <c r="F106">
+        <v>6.09</v>
+      </c>
+      <c r="K106">
+        <v>65.94</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>10448</v>
       </c>
@@ -1962,41 +3069,62 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D107">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>12.89</v>
+      </c>
+      <c r="F107">
+        <v>6.5</v>
+      </c>
+      <c r="K107">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>10448</v>
+        <v>10441</v>
       </c>
       <c r="B108" t="s">
         <v>11</v>
       </c>
       <c r="C108" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I108">
+        <v>25.67</v>
+      </c>
+      <c r="J108">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>10448</v>
+        <v>10441</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I109">
+        <v>25.61</v>
+      </c>
+      <c r="J109">
+        <v>13.08</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>10441</v>
       </c>
@@ -2004,27 +3132,51 @@
         <v>11</v>
       </c>
       <c r="C110" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E110">
+        <v>25.4</v>
+      </c>
+      <c r="F110">
+        <v>9.74</v>
+      </c>
+      <c r="G110">
+        <v>14.25</v>
+      </c>
+      <c r="H110">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>10441</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C111" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D111">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E111">
+        <v>25.4</v>
+      </c>
+      <c r="F111">
+        <v>9.56</v>
+      </c>
+      <c r="G111">
+        <v>14.25</v>
+      </c>
+      <c r="H111">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>10441</v>
       </c>
@@ -2035,10 +3187,22 @@
         <v>14</v>
       </c>
       <c r="D112">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E112">
+        <v>25.4</v>
+      </c>
+      <c r="F112">
+        <v>10.14</v>
+      </c>
+      <c r="G112">
+        <v>14.25</v>
+      </c>
+      <c r="H112">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>10441</v>
       </c>
@@ -2049,38 +3213,74 @@
         <v>14</v>
       </c>
       <c r="D113">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E113">
+        <v>25.4</v>
+      </c>
+      <c r="F113">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="G113">
+        <v>14.25</v>
+      </c>
+      <c r="H113">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>10441</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
       </c>
       <c r="D114">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E114">
+        <v>25.4</v>
+      </c>
+      <c r="F114">
+        <v>10.16</v>
+      </c>
+      <c r="G114">
+        <v>14.25</v>
+      </c>
+      <c r="H114">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>10441</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
       </c>
       <c r="D115">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E115">
+        <v>25.4</v>
+      </c>
+      <c r="F115">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="G115">
+        <v>14.25</v>
+      </c>
+      <c r="H115">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>10441</v>
       </c>
@@ -2091,10 +3291,22 @@
         <v>14</v>
       </c>
       <c r="D116">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E116">
+        <v>25.4</v>
+      </c>
+      <c r="F116">
+        <v>10.32</v>
+      </c>
+      <c r="G116">
+        <v>14.25</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>10441</v>
       </c>
@@ -2105,24 +3317,45 @@
         <v>14</v>
       </c>
       <c r="D117">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E117">
+        <v>25.4</v>
+      </c>
+      <c r="F117">
+        <v>10.42</v>
+      </c>
+      <c r="G117">
+        <v>14.25</v>
+      </c>
+      <c r="H117">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>10441</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C118" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D118">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>12.73</v>
+      </c>
+      <c r="F118">
+        <v>5.48</v>
+      </c>
+      <c r="K118">
+        <v>68.86</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>10441</v>
       </c>
@@ -2130,41 +3363,62 @@
         <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D119">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E119">
+        <v>14.16</v>
+      </c>
+      <c r="F119">
+        <v>7.3</v>
+      </c>
+      <c r="K119">
+        <v>69.48</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>10441</v>
+        <v>10444</v>
       </c>
       <c r="B120" t="s">
         <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I120">
+        <v>25.77</v>
+      </c>
+      <c r="J120">
+        <v>13.08</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>10441</v>
+        <v>10444</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="I121">
+        <v>25.68</v>
+      </c>
+      <c r="J121">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>10444</v>
       </c>
@@ -2172,27 +3426,51 @@
         <v>11</v>
       </c>
       <c r="C122" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E122">
+        <v>25.4</v>
+      </c>
+      <c r="F122">
+        <v>10.8</v>
+      </c>
+      <c r="G122">
+        <v>14.25</v>
+      </c>
+      <c r="H122">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>10444</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C123" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D123">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E123">
+        <v>25.4</v>
+      </c>
+      <c r="F123">
+        <v>11.29</v>
+      </c>
+      <c r="G123">
+        <v>14.25</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>10444</v>
       </c>
@@ -2203,10 +3481,22 @@
         <v>14</v>
       </c>
       <c r="D124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E124">
+        <v>25.4</v>
+      </c>
+      <c r="F124">
+        <v>10.44</v>
+      </c>
+      <c r="G124">
+        <v>14.25</v>
+      </c>
+      <c r="H124">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>10444</v>
       </c>
@@ -2217,38 +3507,74 @@
         <v>14</v>
       </c>
       <c r="D125">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E125">
+        <v>25.4</v>
+      </c>
+      <c r="F125">
+        <v>10.46</v>
+      </c>
+      <c r="G125">
+        <v>14.25</v>
+      </c>
+      <c r="H125">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>10444</v>
       </c>
       <c r="B126" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
         <v>14</v>
       </c>
       <c r="D126">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E126">
+        <v>25.4</v>
+      </c>
+      <c r="F126">
+        <v>9.77</v>
+      </c>
+      <c r="G126">
+        <v>14.25</v>
+      </c>
+      <c r="H126">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>10444</v>
       </c>
       <c r="B127" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
         <v>14</v>
       </c>
       <c r="D127">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E127">
+        <v>25.4</v>
+      </c>
+      <c r="F127">
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="G127">
+        <v>14.25</v>
+      </c>
+      <c r="H127">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>10444</v>
       </c>
@@ -2259,10 +3585,22 @@
         <v>14</v>
       </c>
       <c r="D128">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E128">
+        <v>25.4</v>
+      </c>
+      <c r="F128">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="G128">
+        <v>14.25</v>
+      </c>
+      <c r="H128">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>10444</v>
       </c>
@@ -2273,66 +3611,114 @@
         <v>14</v>
       </c>
       <c r="D129">
+        <v>4</v>
+      </c>
+      <c r="E129">
+        <v>25.4</v>
+      </c>
+      <c r="F129">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="G129">
+        <v>14.25</v>
+      </c>
+      <c r="H129">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>10451</v>
+      </c>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <v>25.55</v>
+      </c>
+      <c r="J130">
+        <v>13.02</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>10451</v>
+      </c>
+      <c r="B131" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="I131">
+        <v>25.44</v>
+      </c>
+      <c r="J131">
+        <v>13.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>10451</v>
+      </c>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>25.4</v>
+      </c>
+      <c r="F132">
+        <v>9.93</v>
+      </c>
+      <c r="G132">
+        <v>14.25</v>
+      </c>
+      <c r="H132">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>10451</v>
+      </c>
+      <c r="B133" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" t="s">
+        <v>14</v>
+      </c>
+      <c r="D133">
         <v>2</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A130">
-        <v>10444</v>
-      </c>
-      <c r="B130" t="s">
-        <v>13</v>
-      </c>
-      <c r="C130" t="s">
-        <v>14</v>
-      </c>
-      <c r="D130">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A131">
-        <v>10444</v>
-      </c>
-      <c r="B131" t="s">
-        <v>13</v>
-      </c>
-      <c r="C131" t="s">
-        <v>14</v>
-      </c>
-      <c r="D131">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A132">
-        <v>10444</v>
-      </c>
-      <c r="B132" t="s">
-        <v>11</v>
-      </c>
-      <c r="C132" t="s">
-        <v>15</v>
-      </c>
-      <c r="D132">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A133">
-        <v>10444</v>
-      </c>
-      <c r="B133" t="s">
-        <v>13</v>
-      </c>
-      <c r="C133" t="s">
-        <v>15</v>
-      </c>
-      <c r="D133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E133">
+        <v>25.4</v>
+      </c>
+      <c r="F133">
+        <v>9.59</v>
+      </c>
+      <c r="G133">
+        <v>14.25</v>
+      </c>
+      <c r="H133">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>10451</v>
       </c>
@@ -2340,32 +3726,56 @@
         <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D134">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E134">
+        <v>25.4</v>
+      </c>
+      <c r="F134">
+        <v>9.81</v>
+      </c>
+      <c r="G134">
+        <v>14.25</v>
+      </c>
+      <c r="H134">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>10451</v>
       </c>
       <c r="B135" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C135" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D135">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E135">
+        <v>25.4</v>
+      </c>
+      <c r="F135">
+        <v>9.52</v>
+      </c>
+      <c r="G135">
+        <v>14.25</v>
+      </c>
+      <c r="H135">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>10451</v>
       </c>
       <c r="B136" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
@@ -2373,13 +3783,25 @@
       <c r="D136">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E136">
+        <v>25.4</v>
+      </c>
+      <c r="F136">
+        <v>8.76</v>
+      </c>
+      <c r="G136">
+        <v>14.25</v>
+      </c>
+      <c r="H136">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>10451</v>
       </c>
       <c r="B137" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
@@ -2387,13 +3809,25 @@
       <c r="D137">
         <v>2</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E137">
+        <v>25.4</v>
+      </c>
+      <c r="F137">
+        <v>9.83</v>
+      </c>
+      <c r="G137">
+        <v>14.25</v>
+      </c>
+      <c r="H137">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>10451</v>
       </c>
       <c r="B138" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
@@ -2401,13 +3835,25 @@
       <c r="D138">
         <v>3</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E138">
+        <v>25.4</v>
+      </c>
+      <c r="F138">
+        <v>9.69</v>
+      </c>
+      <c r="G138">
+        <v>14.25</v>
+      </c>
+      <c r="H138">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>10451</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
@@ -2415,92 +3861,161 @@
       <c r="D139">
         <v>4</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E139">
+        <v>25.4</v>
+      </c>
+      <c r="F139">
+        <v>10.32</v>
+      </c>
+      <c r="G139">
+        <v>14.25</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>10451</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C140" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E140">
+        <v>13.25</v>
+      </c>
+      <c r="F140">
+        <v>5.83</v>
+      </c>
+      <c r="K140">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>10451</v>
+        <v>10458</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="I141">
+        <v>23.94</v>
+      </c>
+      <c r="J141">
+        <v>12.88</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>10458</v>
+      </c>
+      <c r="B142" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="I142">
+        <v>24.9</v>
+      </c>
+      <c r="J142">
+        <v>12.89</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>10458</v>
+      </c>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" t="s">
+        <v>14</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>25.4</v>
+      </c>
+      <c r="F143">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="G143">
+        <v>14.25</v>
+      </c>
+      <c r="H143">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>10458</v>
+      </c>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144">
         <v>2</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A142">
-        <v>10451</v>
-      </c>
-      <c r="B142" t="s">
-        <v>13</v>
-      </c>
-      <c r="C142" t="s">
-        <v>14</v>
-      </c>
-      <c r="D142">
+      <c r="E144">
+        <v>25.4</v>
+      </c>
+      <c r="F144">
+        <v>9.6</v>
+      </c>
+      <c r="G144">
+        <v>14.25</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>10458</v>
+      </c>
+      <c r="B145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145">
         <v>3</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A143">
-        <v>10451</v>
-      </c>
-      <c r="B143" t="s">
-        <v>13</v>
-      </c>
-      <c r="C143" t="s">
-        <v>14</v>
-      </c>
-      <c r="D143">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A144">
-        <v>10451</v>
-      </c>
-      <c r="B144" t="s">
-        <v>11</v>
-      </c>
-      <c r="C144" t="s">
-        <v>15</v>
-      </c>
-      <c r="D144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A145">
-        <v>10451</v>
-      </c>
-      <c r="B145" t="s">
-        <v>13</v>
-      </c>
-      <c r="C145" t="s">
-        <v>15</v>
-      </c>
-      <c r="D145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E145">
+        <v>25.4</v>
+      </c>
+      <c r="F145">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="G145">
+        <v>14.25</v>
+      </c>
+      <c r="H145">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>10458</v>
       </c>
@@ -2508,13 +4023,25 @@
         <v>11</v>
       </c>
       <c r="C146" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E146">
+        <v>25.4</v>
+      </c>
+      <c r="F146">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="G146">
+        <v>14.25</v>
+      </c>
+      <c r="H146">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>10458</v>
       </c>
@@ -2522,55 +4049,103 @@
         <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D147">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E147">
+        <v>25.4</v>
+      </c>
+      <c r="F147">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="G147">
+        <v>14.25</v>
+      </c>
+      <c r="H147">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>10458</v>
       </c>
       <c r="B148" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
       </c>
       <c r="D148">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E148">
+        <v>25.4</v>
+      </c>
+      <c r="F148">
+        <v>9.92</v>
+      </c>
+      <c r="G148">
+        <v>14.25</v>
+      </c>
+      <c r="H148">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>10458</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
         <v>14</v>
       </c>
       <c r="D149">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E149">
+        <v>25.4</v>
+      </c>
+      <c r="F149">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="G149">
+        <v>14.25</v>
+      </c>
+      <c r="H149">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>10458</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
       </c>
       <c r="D150">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E150">
+        <v>25.4</v>
+      </c>
+      <c r="F150">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="G150">
+        <v>14.25</v>
+      </c>
+      <c r="H150">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>10458</v>
       </c>
@@ -2578,13 +4153,22 @@
         <v>11</v>
       </c>
       <c r="C151" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D151">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E151">
+        <v>12.63</v>
+      </c>
+      <c r="F151">
+        <v>6.32</v>
+      </c>
+      <c r="K151">
+        <v>65.650000000000006</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>10458</v>
       </c>
@@ -2592,83 +4176,140 @@
         <v>13</v>
       </c>
       <c r="C152" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E152">
+        <v>13.99</v>
+      </c>
+      <c r="F152">
+        <v>6.57</v>
+      </c>
+      <c r="K152">
+        <v>66.92</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>10458</v>
+        <v>10445</v>
       </c>
       <c r="B153" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C153" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="I153">
+        <v>25.83</v>
+      </c>
+      <c r="J153">
+        <v>13.08</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>10445</v>
+      </c>
+      <c r="B154" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+      <c r="I154">
+        <v>25.65</v>
+      </c>
+      <c r="J154">
+        <v>13.05</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>10445</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" t="s">
+        <v>14</v>
+      </c>
+      <c r="D155">
+        <v>1</v>
+      </c>
+      <c r="E155">
+        <v>25.4</v>
+      </c>
+      <c r="F155">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G155">
+        <v>14.25</v>
+      </c>
+      <c r="H155">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>10445</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" t="s">
+        <v>14</v>
+      </c>
+      <c r="D156">
         <v>2</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A154">
-        <v>10458</v>
-      </c>
-      <c r="B154" t="s">
-        <v>13</v>
-      </c>
-      <c r="C154" t="s">
-        <v>14</v>
-      </c>
-      <c r="D154">
+      <c r="E156">
+        <v>25.4</v>
+      </c>
+      <c r="F156">
+        <v>10.11</v>
+      </c>
+      <c r="G156">
+        <v>14.25</v>
+      </c>
+      <c r="H156">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>10445</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" t="s">
+        <v>14</v>
+      </c>
+      <c r="D157">
         <v>3</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A155">
-        <v>10458</v>
-      </c>
-      <c r="B155" t="s">
-        <v>13</v>
-      </c>
-      <c r="C155" t="s">
-        <v>14</v>
-      </c>
-      <c r="D155">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A156">
-        <v>10458</v>
-      </c>
-      <c r="B156" t="s">
-        <v>11</v>
-      </c>
-      <c r="C156" t="s">
-        <v>15</v>
-      </c>
-      <c r="D156">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A157">
-        <v>10458</v>
-      </c>
-      <c r="B157" t="s">
-        <v>13</v>
-      </c>
-      <c r="C157" t="s">
-        <v>15</v>
-      </c>
-      <c r="D157">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E157">
+        <v>25.4</v>
+      </c>
+      <c r="F157">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="G157">
+        <v>14.25</v>
+      </c>
+      <c r="H157">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>10445</v>
       </c>
@@ -2676,13 +4317,25 @@
         <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D158">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E158">
+        <v>25.4</v>
+      </c>
+      <c r="F158">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="G158">
+        <v>14.25</v>
+      </c>
+      <c r="H158">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>10445</v>
       </c>
@@ -2690,55 +4343,103 @@
         <v>13</v>
       </c>
       <c r="C159" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D159">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E159">
+        <v>25.4</v>
+      </c>
+      <c r="F159">
+        <v>9.81</v>
+      </c>
+      <c r="G159">
+        <v>14.25</v>
+      </c>
+      <c r="H159">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>10445</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
         <v>14</v>
       </c>
       <c r="D160">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E160">
+        <v>25.4</v>
+      </c>
+      <c r="F160">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="G160">
+        <v>14.25</v>
+      </c>
+      <c r="H160">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>10445</v>
       </c>
       <c r="B161" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C161" t="s">
         <v>14</v>
       </c>
       <c r="D161">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E161">
+        <v>25.4</v>
+      </c>
+      <c r="F161">
+        <v>9.58</v>
+      </c>
+      <c r="G161">
+        <v>14.25</v>
+      </c>
+      <c r="H161">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>10445</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C162" t="s">
         <v>14</v>
       </c>
       <c r="D162">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E162">
+        <v>25.4</v>
+      </c>
+      <c r="F162">
+        <v>9.33</v>
+      </c>
+      <c r="G162">
+        <v>14.25</v>
+      </c>
+      <c r="H162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>10445</v>
       </c>
@@ -2746,13 +4447,22 @@
         <v>11</v>
       </c>
       <c r="C163" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D163">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E163">
+        <v>13.44</v>
+      </c>
+      <c r="F163">
+        <v>5.71</v>
+      </c>
+      <c r="K163">
+        <v>73.27</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>10445</v>
       </c>
@@ -2760,80 +4470,1172 @@
         <v>13</v>
       </c>
       <c r="C164" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="E164">
+        <v>13.56</v>
+      </c>
+      <c r="F164">
+        <v>6.39</v>
+      </c>
+      <c r="K164">
+        <v>72.41</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>10445</v>
+        <v>10446</v>
       </c>
       <c r="B165" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C165" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D165">
+        <v>1</v>
+      </c>
+      <c r="I165">
+        <v>25.61</v>
+      </c>
+      <c r="J165">
+        <v>13.06</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>10446</v>
+      </c>
+      <c r="B166" t="s">
+        <v>13</v>
+      </c>
+      <c r="C166" t="s">
+        <v>12</v>
+      </c>
+      <c r="D166">
+        <v>1</v>
+      </c>
+      <c r="I166">
+        <v>25.83</v>
+      </c>
+      <c r="J166">
+        <v>13.06</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>10446</v>
+      </c>
+      <c r="B167" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" t="s">
+        <v>14</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+      <c r="E167">
+        <v>25.4</v>
+      </c>
+      <c r="F167">
+        <v>10.5</v>
+      </c>
+      <c r="G167">
+        <v>14.25</v>
+      </c>
+      <c r="H167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>10446</v>
+      </c>
+      <c r="B168" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168" t="s">
+        <v>14</v>
+      </c>
+      <c r="D168">
         <v>2</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A166">
-        <v>10445</v>
-      </c>
-      <c r="B166" t="s">
-        <v>13</v>
-      </c>
-      <c r="C166" t="s">
-        <v>14</v>
-      </c>
-      <c r="D166">
+      <c r="E168">
+        <v>25.4</v>
+      </c>
+      <c r="F168">
+        <v>10.5</v>
+      </c>
+      <c r="G168">
+        <v>14.25</v>
+      </c>
+      <c r="H168">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>10446</v>
+      </c>
+      <c r="B169" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" t="s">
+        <v>14</v>
+      </c>
+      <c r="D169">
         <v>3</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A167">
-        <v>10445</v>
-      </c>
-      <c r="B167" t="s">
-        <v>13</v>
-      </c>
-      <c r="C167" t="s">
-        <v>14</v>
-      </c>
-      <c r="D167">
+      <c r="E169">
+        <v>25.4</v>
+      </c>
+      <c r="F169">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="G169">
+        <v>14.25</v>
+      </c>
+      <c r="H169">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>10446</v>
+      </c>
+      <c r="B170" t="s">
+        <v>11</v>
+      </c>
+      <c r="C170" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170">
         <v>4</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A168">
-        <v>10445</v>
-      </c>
-      <c r="B168" t="s">
-        <v>11</v>
-      </c>
-      <c r="C168" t="s">
+      <c r="E170">
+        <v>25.4</v>
+      </c>
+      <c r="F170">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="G170">
+        <v>14.25</v>
+      </c>
+      <c r="H170">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>10446</v>
+      </c>
+      <c r="B171" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171" t="s">
+        <v>14</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171">
+        <v>25.4</v>
+      </c>
+      <c r="F171">
+        <v>10.64</v>
+      </c>
+      <c r="G171">
+        <v>14.25</v>
+      </c>
+      <c r="H171">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>10446</v>
+      </c>
+      <c r="B172" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172">
+        <v>2</v>
+      </c>
+      <c r="E172">
+        <v>25.4</v>
+      </c>
+      <c r="F172">
+        <v>9.81</v>
+      </c>
+      <c r="G172">
+        <v>14.25</v>
+      </c>
+      <c r="H172">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>10446</v>
+      </c>
+      <c r="B173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" t="s">
+        <v>14</v>
+      </c>
+      <c r="D173">
+        <v>3</v>
+      </c>
+      <c r="E173">
+        <v>25.4</v>
+      </c>
+      <c r="F173">
+        <v>10.01</v>
+      </c>
+      <c r="G173">
+        <v>14.25</v>
+      </c>
+      <c r="H173">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>10446</v>
+      </c>
+      <c r="B174" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" t="s">
+        <v>14</v>
+      </c>
+      <c r="D174">
+        <v>4</v>
+      </c>
+      <c r="E174">
+        <v>25.4</v>
+      </c>
+      <c r="F174">
+        <v>10.15</v>
+      </c>
+      <c r="G174">
+        <v>14.25</v>
+      </c>
+      <c r="H174">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>10446</v>
+      </c>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" t="s">
         <v>15</v>
       </c>
-      <c r="D168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="14" x14ac:dyDescent="0.3">
-      <c r="A169">
-        <v>10445</v>
-      </c>
-      <c r="B169" t="s">
-        <v>13</v>
-      </c>
-      <c r="C169" t="s">
+      <c r="D175">
+        <v>1</v>
+      </c>
+      <c r="E175">
+        <v>13.01</v>
+      </c>
+      <c r="F175">
+        <v>6.79</v>
+      </c>
+      <c r="K175">
+        <v>64.489999999999995</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>10446</v>
+      </c>
+      <c r="B176" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176" t="s">
         <v>15</v>
       </c>
-      <c r="D169">
-        <v>1</v>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176">
+        <v>12.18</v>
+      </c>
+      <c r="F176">
+        <v>5.26</v>
+      </c>
+      <c r="K176">
+        <v>65.84</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>10454</v>
+      </c>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>12</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
+      </c>
+      <c r="I177">
+        <v>25.65</v>
+      </c>
+      <c r="J177">
+        <v>12.92</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>10454</v>
+      </c>
+      <c r="B178" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" t="s">
+        <v>12</v>
+      </c>
+      <c r="D178">
+        <v>1</v>
+      </c>
+      <c r="I178">
+        <v>25.53</v>
+      </c>
+      <c r="J178">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>10454</v>
+      </c>
+      <c r="B179" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="E179">
+        <v>25.4</v>
+      </c>
+      <c r="F179">
+        <v>10.19</v>
+      </c>
+      <c r="G179">
+        <v>14.25</v>
+      </c>
+      <c r="H179">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>10454</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180">
+        <v>2</v>
+      </c>
+      <c r="E180">
+        <v>25.4</v>
+      </c>
+      <c r="F180">
+        <v>10.17</v>
+      </c>
+      <c r="G180">
+        <v>14.25</v>
+      </c>
+      <c r="H180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>10454</v>
+      </c>
+      <c r="B181" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181">
+        <v>3</v>
+      </c>
+      <c r="E181">
+        <v>25.4</v>
+      </c>
+      <c r="F181">
+        <v>9.82</v>
+      </c>
+      <c r="G181">
+        <v>14.25</v>
+      </c>
+      <c r="H181">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>10454</v>
+      </c>
+      <c r="B182" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182">
+        <v>4</v>
+      </c>
+      <c r="E182">
+        <v>25.4</v>
+      </c>
+      <c r="F182">
+        <v>9.94</v>
+      </c>
+      <c r="G182">
+        <v>14.25</v>
+      </c>
+      <c r="H182">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>10454</v>
+      </c>
+      <c r="B183" t="s">
+        <v>13</v>
+      </c>
+      <c r="C183" t="s">
+        <v>14</v>
+      </c>
+      <c r="D183">
+        <v>1</v>
+      </c>
+      <c r="E183">
+        <v>25.4</v>
+      </c>
+      <c r="F183">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="G183">
+        <v>14.25</v>
+      </c>
+      <c r="H183">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>10454</v>
+      </c>
+      <c r="B184" t="s">
+        <v>13</v>
+      </c>
+      <c r="C184" t="s">
+        <v>14</v>
+      </c>
+      <c r="D184">
+        <v>2</v>
+      </c>
+      <c r="E184">
+        <v>25.4</v>
+      </c>
+      <c r="F184">
+        <v>9.25</v>
+      </c>
+      <c r="G184">
+        <v>14.25</v>
+      </c>
+      <c r="H184">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>10454</v>
+      </c>
+      <c r="B185" t="s">
+        <v>13</v>
+      </c>
+      <c r="C185" t="s">
+        <v>14</v>
+      </c>
+      <c r="D185">
+        <v>3</v>
+      </c>
+      <c r="E185">
+        <v>25.4</v>
+      </c>
+      <c r="F185">
+        <v>9.49</v>
+      </c>
+      <c r="G185">
+        <v>14.25</v>
+      </c>
+      <c r="H185">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>10454</v>
+      </c>
+      <c r="B186" t="s">
+        <v>13</v>
+      </c>
+      <c r="C186" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186">
+        <v>4</v>
+      </c>
+      <c r="E186">
+        <v>25.4</v>
+      </c>
+      <c r="F186">
+        <v>10.02</v>
+      </c>
+      <c r="G186">
+        <v>14.25</v>
+      </c>
+      <c r="H186">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>10454</v>
+      </c>
+      <c r="B187" t="s">
+        <v>13</v>
+      </c>
+      <c r="C187" t="s">
+        <v>15</v>
+      </c>
+      <c r="D187">
+        <v>1</v>
+      </c>
+      <c r="E187">
+        <v>12.77</v>
+      </c>
+      <c r="F187">
+        <v>5.83</v>
+      </c>
+      <c r="K187">
+        <v>82.03</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>10452</v>
+      </c>
+      <c r="B188" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" t="s">
+        <v>12</v>
+      </c>
+      <c r="D188">
+        <v>1</v>
+      </c>
+      <c r="I188">
+        <v>25.73</v>
+      </c>
+      <c r="J188">
+        <v>13.02</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>10452</v>
+      </c>
+      <c r="B189" t="s">
+        <v>13</v>
+      </c>
+      <c r="C189" t="s">
+        <v>12</v>
+      </c>
+      <c r="D189">
+        <v>1</v>
+      </c>
+      <c r="I189">
+        <v>25.99</v>
+      </c>
+      <c r="J189">
+        <v>13.03</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>10452</v>
+      </c>
+      <c r="B190" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" t="s">
+        <v>14</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190">
+        <v>25.4</v>
+      </c>
+      <c r="F190">
+        <v>9.65</v>
+      </c>
+      <c r="G190">
+        <v>14.25</v>
+      </c>
+      <c r="H190">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>10452</v>
+      </c>
+      <c r="B191" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" t="s">
+        <v>14</v>
+      </c>
+      <c r="D191">
+        <v>2</v>
+      </c>
+      <c r="E191">
+        <v>25.4</v>
+      </c>
+      <c r="F191">
+        <v>10.82</v>
+      </c>
+      <c r="G191">
+        <v>14.25</v>
+      </c>
+      <c r="H191">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>10452</v>
+      </c>
+      <c r="B192" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" t="s">
+        <v>14</v>
+      </c>
+      <c r="D192">
+        <v>3</v>
+      </c>
+      <c r="E192">
+        <v>25.4</v>
+      </c>
+      <c r="F192">
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="G192">
+        <v>14.25</v>
+      </c>
+      <c r="H192">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>10452</v>
+      </c>
+      <c r="B193" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" t="s">
+        <v>14</v>
+      </c>
+      <c r="D193">
+        <v>4</v>
+      </c>
+      <c r="E193">
+        <v>25.4</v>
+      </c>
+      <c r="F193">
+        <v>9.69</v>
+      </c>
+      <c r="G193">
+        <v>14.25</v>
+      </c>
+      <c r="H193">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>10452</v>
+      </c>
+      <c r="B194" t="s">
+        <v>13</v>
+      </c>
+      <c r="C194" t="s">
+        <v>14</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194">
+        <v>25.4</v>
+      </c>
+      <c r="F194">
+        <v>9.19</v>
+      </c>
+      <c r="G194">
+        <v>14.25</v>
+      </c>
+      <c r="H194">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>10452</v>
+      </c>
+      <c r="B195" t="s">
+        <v>13</v>
+      </c>
+      <c r="C195" t="s">
+        <v>14</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195">
+        <v>25.4</v>
+      </c>
+      <c r="F195">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="G195">
+        <v>14.25</v>
+      </c>
+      <c r="H195">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>10452</v>
+      </c>
+      <c r="B196" t="s">
+        <v>13</v>
+      </c>
+      <c r="C196" t="s">
+        <v>14</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196">
+        <v>25.4</v>
+      </c>
+      <c r="F196">
+        <v>9.51</v>
+      </c>
+      <c r="G196">
+        <v>14.25</v>
+      </c>
+      <c r="H196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>10452</v>
+      </c>
+      <c r="B197" t="s">
+        <v>13</v>
+      </c>
+      <c r="C197" t="s">
+        <v>14</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197">
+        <v>25.4</v>
+      </c>
+      <c r="F197">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="G197">
+        <v>14.25</v>
+      </c>
+      <c r="H197">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>10452</v>
+      </c>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" t="s">
+        <v>15</v>
+      </c>
+      <c r="D198">
+        <v>1</v>
+      </c>
+      <c r="E198">
+        <v>13.31</v>
+      </c>
+      <c r="F198">
+        <v>6.23</v>
+      </c>
+      <c r="K198">
+        <v>69.73</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>10452</v>
+      </c>
+      <c r="B199" t="s">
+        <v>13</v>
+      </c>
+      <c r="C199" t="s">
+        <v>15</v>
+      </c>
+      <c r="D199">
+        <v>1</v>
+      </c>
+      <c r="E199">
+        <v>13.15</v>
+      </c>
+      <c r="F199">
+        <v>5.74</v>
+      </c>
+      <c r="K199">
+        <v>68.52</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>10456</v>
+      </c>
+      <c r="B200" t="s">
+        <v>11</v>
+      </c>
+      <c r="C200" t="s">
+        <v>12</v>
+      </c>
+      <c r="D200">
+        <v>1</v>
+      </c>
+      <c r="I200">
+        <v>25.5</v>
+      </c>
+      <c r="J200">
+        <v>12.98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>10456</v>
+      </c>
+      <c r="B201" t="s">
+        <v>13</v>
+      </c>
+      <c r="C201" t="s">
+        <v>12</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+      <c r="I201">
+        <v>25.18</v>
+      </c>
+      <c r="J201">
+        <v>13.06</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>10456</v>
+      </c>
+      <c r="B202" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" t="s">
+        <v>14</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202">
+        <v>25.4</v>
+      </c>
+      <c r="F202">
+        <v>9.32</v>
+      </c>
+      <c r="G202">
+        <v>14.25</v>
+      </c>
+      <c r="H202">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>10456</v>
+      </c>
+      <c r="B203" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" t="s">
+        <v>14</v>
+      </c>
+      <c r="D203">
+        <v>2</v>
+      </c>
+      <c r="E203">
+        <v>25.4</v>
+      </c>
+      <c r="F203">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="G203">
+        <v>14.25</v>
+      </c>
+      <c r="H203">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>10456</v>
+      </c>
+      <c r="B204" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" t="s">
+        <v>14</v>
+      </c>
+      <c r="D204">
+        <v>3</v>
+      </c>
+      <c r="E204">
+        <v>25.4</v>
+      </c>
+      <c r="F204">
+        <v>9.74</v>
+      </c>
+      <c r="G204">
+        <v>14.25</v>
+      </c>
+      <c r="H204">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>10456</v>
+      </c>
+      <c r="B205" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" t="s">
+        <v>14</v>
+      </c>
+      <c r="D205">
+        <v>4</v>
+      </c>
+      <c r="E205">
+        <v>25.4</v>
+      </c>
+      <c r="F205">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="G205">
+        <v>14.25</v>
+      </c>
+      <c r="H205">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>10456</v>
+      </c>
+      <c r="B206" t="s">
+        <v>13</v>
+      </c>
+      <c r="C206" t="s">
+        <v>14</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>25.4</v>
+      </c>
+      <c r="F206">
+        <v>10.51</v>
+      </c>
+      <c r="G206">
+        <v>14.25</v>
+      </c>
+      <c r="H206">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>10456</v>
+      </c>
+      <c r="B207" t="s">
+        <v>13</v>
+      </c>
+      <c r="C207" t="s">
+        <v>14</v>
+      </c>
+      <c r="D207">
+        <v>2</v>
+      </c>
+      <c r="E207">
+        <v>25.4</v>
+      </c>
+      <c r="F207">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="G207">
+        <v>14.25</v>
+      </c>
+      <c r="H207">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>10456</v>
+      </c>
+      <c r="B208" t="s">
+        <v>13</v>
+      </c>
+      <c r="C208" t="s">
+        <v>14</v>
+      </c>
+      <c r="D208">
+        <v>3</v>
+      </c>
+      <c r="E208">
+        <v>25.4</v>
+      </c>
+      <c r="F208">
+        <v>10.07</v>
+      </c>
+      <c r="G208">
+        <v>14.25</v>
+      </c>
+      <c r="H208">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>10456</v>
+      </c>
+      <c r="B209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" t="s">
+        <v>14</v>
+      </c>
+      <c r="D209">
+        <v>4</v>
+      </c>
+      <c r="E209">
+        <v>25.4</v>
+      </c>
+      <c r="F209">
+        <v>9.91</v>
+      </c>
+      <c r="G209">
+        <v>14.25</v>
+      </c>
+      <c r="H209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>10456</v>
+      </c>
+      <c r="B210" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" t="s">
+        <v>15</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="E210">
+        <v>15.4</v>
+      </c>
+      <c r="F210">
+        <v>6.73</v>
+      </c>
+      <c r="K210">
+        <v>91.54</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>10456</v>
+      </c>
+      <c r="B211" t="s">
+        <v>13</v>
+      </c>
+      <c r="C211" t="s">
+        <v>15</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211">
+        <v>12.85</v>
+      </c>
+      <c r="F211">
+        <v>5.61</v>
+      </c>
+      <c r="K211">
+        <v>91.07</v>
       </c>
     </row>
   </sheetData>
@@ -2843,13 +5645,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K217"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K211"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2884,7 +5686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10448</v>
       </c>
@@ -2897,8 +5699,15 @@
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <v>25.72</v>
+      </c>
+      <c r="J2">
+        <v>12.93</v>
+      </c>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10448</v>
       </c>
@@ -2911,8 +5720,15 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="I3">
+        <v>25.79</v>
+      </c>
+      <c r="J3">
+        <v>12.89</v>
+      </c>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>10448</v>
       </c>
@@ -2925,8 +5741,21 @@
       <c r="D4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>25.4</v>
+      </c>
+      <c r="F4">
+        <v>9.73</v>
+      </c>
+      <c r="G4">
+        <v>14.25</v>
+      </c>
+      <c r="H4">
+        <v>0.7</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>10448</v>
       </c>
@@ -2939,8 +5768,21 @@
       <c r="D5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>25.4</v>
+      </c>
+      <c r="F5">
+        <v>9.91</v>
+      </c>
+      <c r="G5">
+        <v>14.25</v>
+      </c>
+      <c r="H5">
+        <v>1.3</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>10448</v>
       </c>
@@ -2953,8 +5795,21 @@
       <c r="D6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>25.4</v>
+      </c>
+      <c r="F6">
+        <v>9.84</v>
+      </c>
+      <c r="G6">
+        <v>14.25</v>
+      </c>
+      <c r="H6">
+        <v>1.2</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>10448</v>
       </c>
@@ -2967,8 +5822,21 @@
       <c r="D7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>25.4</v>
+      </c>
+      <c r="F7">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="G7">
+        <v>14.25</v>
+      </c>
+      <c r="H7">
+        <v>0.8</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>10448</v>
       </c>
@@ -2981,8 +5849,21 @@
       <c r="D8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>25.4</v>
+      </c>
+      <c r="F8">
+        <v>10.1</v>
+      </c>
+      <c r="G8">
+        <v>14.25</v>
+      </c>
+      <c r="H8">
+        <v>0.6</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>10448</v>
       </c>
@@ -2995,8 +5876,21 @@
       <c r="D9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>25.4</v>
+      </c>
+      <c r="F9">
+        <v>9.83</v>
+      </c>
+      <c r="G9">
+        <v>14.25</v>
+      </c>
+      <c r="H9">
+        <v>0.9</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10448</v>
       </c>
@@ -3009,8 +5903,21 @@
       <c r="D10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>25.4</v>
+      </c>
+      <c r="F10">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="G10">
+        <v>14.25</v>
+      </c>
+      <c r="H10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10448</v>
       </c>
@@ -3023,8 +5930,21 @@
       <c r="D11">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <v>25.4</v>
+      </c>
+      <c r="F11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G11">
+        <v>14.25</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10448</v>
       </c>
@@ -3037,8 +5957,17 @@
       <c r="D12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E12">
+        <v>13.08</v>
+      </c>
+      <c r="F12">
+        <v>5.49</v>
+      </c>
+      <c r="K12">
+        <v>77.819999999999993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10448</v>
       </c>
@@ -3051,8 +5980,17 @@
       <c r="D13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E13">
+        <v>12.75</v>
+      </c>
+      <c r="F13">
+        <v>7.73</v>
+      </c>
+      <c r="K13">
+        <v>76.64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>10453</v>
       </c>
@@ -3072,7 +6010,7 @@
         <v>12.93</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>10453</v>
       </c>
@@ -3092,7 +6030,7 @@
         <v>12.89</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>10453</v>
       </c>
@@ -3118,7 +6056,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>10453</v>
       </c>
@@ -3144,7 +6082,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>10453</v>
       </c>
@@ -3170,7 +6108,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>10453</v>
       </c>
@@ -3196,7 +6134,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>10453</v>
       </c>
@@ -3222,7 +6160,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>10453</v>
       </c>
@@ -3248,7 +6186,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>10453</v>
       </c>
@@ -3274,7 +6212,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>10453</v>
       </c>
@@ -3300,7 +6238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>10453</v>
       </c>
@@ -3323,7 +6261,7 @@
         <v>77.819999999999993</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>10453</v>
       </c>
@@ -3346,7 +6284,7 @@
         <v>76.64</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>10457</v>
       </c>
@@ -3366,7 +6304,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>10457</v>
       </c>
@@ -3386,7 +6324,7 @@
         <v>13.06</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>10457</v>
       </c>
@@ -3412,7 +6350,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>10457</v>
       </c>
@@ -3438,7 +6376,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>10457</v>
       </c>
@@ -3464,7 +6402,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>10457</v>
       </c>
@@ -3490,7 +6428,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>10457</v>
       </c>
@@ -3516,7 +6454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>10457</v>
       </c>
@@ -3542,7 +6480,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>10457</v>
       </c>
@@ -3568,7 +6506,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>10457</v>
       </c>
@@ -3594,7 +6532,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>10446</v>
       </c>
@@ -3614,7 +6552,7 @@
         <v>13.06</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>10446</v>
       </c>
@@ -3634,7 +6572,7 @@
         <v>13.03</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>10446</v>
       </c>
@@ -3660,7 +6598,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>10446</v>
       </c>
@@ -3686,7 +6624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>10446</v>
       </c>
@@ -3712,7 +6650,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>10446</v>
       </c>
@@ -3738,7 +6676,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>10446</v>
       </c>
@@ -3764,7 +6702,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>10446</v>
       </c>
@@ -3790,7 +6728,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>10446</v>
       </c>
@@ -3816,7 +6754,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>10446</v>
       </c>
@@ -3842,7 +6780,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>10446</v>
       </c>
@@ -3865,7 +6803,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>10446</v>
       </c>
@@ -3888,7 +6826,7 @@
         <v>76.64</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>10456</v>
       </c>
@@ -3908,7 +6846,7 @@
         <v>12.88</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>10456</v>
       </c>
@@ -3928,7 +6866,7 @@
         <v>13.14</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>10456</v>
       </c>
@@ -3954,7 +6892,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>10456</v>
       </c>
@@ -3980,7 +6918,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>10456</v>
       </c>
@@ -4006,7 +6944,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>10456</v>
       </c>
@@ -4032,7 +6970,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>10456</v>
       </c>
@@ -4058,7 +6996,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>10456</v>
       </c>
@@ -4084,7 +7022,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>10456</v>
       </c>
@@ -4110,7 +7048,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>10456</v>
       </c>
@@ -4136,7 +7074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>10456</v>
       </c>
@@ -4159,7 +7097,7 @@
         <v>72.39</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>10456</v>
       </c>
@@ -4182,7 +7120,7 @@
         <v>78.61</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>10454</v>
       </c>
@@ -4202,7 +7140,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>10454</v>
       </c>
@@ -4222,7 +7160,7 @@
         <v>12.88</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>10454</v>
       </c>
@@ -4248,7 +7186,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>10454</v>
       </c>
@@ -4274,7 +7212,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>10454</v>
       </c>
@@ -4300,7 +7238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>10454</v>
       </c>
@@ -4326,7 +7264,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>10454</v>
       </c>
@@ -4352,7 +7290,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>10454</v>
       </c>
@@ -4378,7 +7316,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>10454</v>
       </c>
@@ -4404,7 +7342,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>10454</v>
       </c>
@@ -4430,7 +7368,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>10454</v>
       </c>
@@ -4453,7 +7391,7 @@
         <v>70.260000000000005</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>10449</v>
       </c>
@@ -4466,8 +7404,14 @@
       <c r="D71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="I71">
+        <v>25.52</v>
+      </c>
+      <c r="J71">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>10449</v>
       </c>
@@ -4480,8 +7424,14 @@
       <c r="D72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <v>25.21</v>
+      </c>
+      <c r="J72">
+        <v>13.06</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>10449</v>
       </c>
@@ -4494,8 +7444,20 @@
       <c r="D73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E73">
+        <v>25.4</v>
+      </c>
+      <c r="F73">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="G73">
+        <v>14.25</v>
+      </c>
+      <c r="H73">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>10449</v>
       </c>
@@ -4508,8 +7470,20 @@
       <c r="D74">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E74">
+        <v>25.4</v>
+      </c>
+      <c r="F74">
+        <v>9.4</v>
+      </c>
+      <c r="G74">
+        <v>14.25</v>
+      </c>
+      <c r="H74">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>10449</v>
       </c>
@@ -4522,8 +7496,20 @@
       <c r="D75">
         <v>3</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E75">
+        <v>25.4</v>
+      </c>
+      <c r="F75">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="G75">
+        <v>14.25</v>
+      </c>
+      <c r="H75">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>10449</v>
       </c>
@@ -4536,8 +7522,20 @@
       <c r="D76">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E76">
+        <v>25.4</v>
+      </c>
+      <c r="F76">
+        <v>9.86</v>
+      </c>
+      <c r="G76">
+        <v>14.25</v>
+      </c>
+      <c r="H76">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>10449</v>
       </c>
@@ -4550,8 +7548,20 @@
       <c r="D77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E77">
+        <v>25.4</v>
+      </c>
+      <c r="F77">
+        <v>11.06</v>
+      </c>
+      <c r="G77">
+        <v>14.25</v>
+      </c>
+      <c r="H77">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>10449</v>
       </c>
@@ -4564,8 +7574,20 @@
       <c r="D78">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E78">
+        <v>25.4</v>
+      </c>
+      <c r="F78">
+        <v>9.25</v>
+      </c>
+      <c r="G78">
+        <v>14.25</v>
+      </c>
+      <c r="H78">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>10449</v>
       </c>
@@ -4578,8 +7600,20 @@
       <c r="D79">
         <v>3</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E79">
+        <v>25.4</v>
+      </c>
+      <c r="F79">
+        <v>10.76</v>
+      </c>
+      <c r="G79">
+        <v>14.25</v>
+      </c>
+      <c r="H79">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>10449</v>
       </c>
@@ -4592,8 +7626,20 @@
       <c r="D80">
         <v>4</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E80">
+        <v>25.4</v>
+      </c>
+      <c r="F80">
+        <v>10.52</v>
+      </c>
+      <c r="G80">
+        <v>14.25</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>10449</v>
       </c>
@@ -4606,8 +7652,17 @@
       <c r="D81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E81">
+        <v>13.02</v>
+      </c>
+      <c r="F81">
+        <v>5.94</v>
+      </c>
+      <c r="K81">
+        <v>65.900000000000006</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>10449</v>
       </c>
@@ -4620,8 +7675,17 @@
       <c r="D82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="E82">
+        <v>12.43</v>
+      </c>
+      <c r="F82">
+        <v>6.21</v>
+      </c>
+      <c r="K82">
+        <v>67.78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>10440</v>
       </c>
@@ -4641,7 +7705,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>10440</v>
       </c>
@@ -4661,7 +7725,7 @@
         <v>13.06</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>10440</v>
       </c>
@@ -4687,7 +7751,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>10440</v>
       </c>
@@ -4713,7 +7777,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>10440</v>
       </c>
@@ -4739,7 +7803,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>10440</v>
       </c>
@@ -4765,7 +7829,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>10440</v>
       </c>
@@ -4791,7 +7855,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>10440</v>
       </c>
@@ -4817,7 +7881,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>10440</v>
       </c>
@@ -4843,7 +7907,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>10440</v>
       </c>
@@ -4869,7 +7933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>10440</v>
       </c>
@@ -4892,7 +7956,7 @@
         <v>65.900000000000006</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>10440</v>
       </c>
@@ -4915,7 +7979,7 @@
         <v>67.78</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>10443</v>
       </c>
@@ -4935,7 +7999,7 @@
         <v>12.88</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>10443</v>
       </c>
@@ -4955,7 +8019,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>10443</v>
       </c>
@@ -4981,7 +8045,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>10443</v>
       </c>
@@ -5007,7 +8071,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>10443</v>
       </c>
@@ -5033,7 +8097,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>10443</v>
       </c>
@@ -5059,7 +8123,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>10443</v>
       </c>
@@ -5085,7 +8149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>10443</v>
       </c>
@@ -5111,7 +8175,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>10443</v>
       </c>
@@ -5137,7 +8201,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>10443</v>
       </c>
@@ -5163,7 +8227,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>10443</v>
       </c>
@@ -5186,7 +8250,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>10443</v>
       </c>
@@ -5209,7 +8273,7 @@
         <v>67.05</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>10442</v>
       </c>
@@ -5229,7 +8293,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>10442</v>
       </c>
@@ -5249,7 +8313,7 @@
         <v>12.87</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>10442</v>
       </c>
@@ -5275,7 +8339,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>10442</v>
       </c>
@@ -5301,7 +8365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>10442</v>
       </c>
@@ -5327,7 +8391,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>10442</v>
       </c>
@@ -5353,7 +8417,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>10442</v>
       </c>
@@ -5379,7 +8443,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>10442</v>
       </c>
@@ -5405,7 +8469,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>10442</v>
       </c>
@@ -5431,7 +8495,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>10442</v>
       </c>
@@ -5457,7 +8521,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>10442</v>
       </c>
@@ -5480,7 +8544,7 @@
         <v>70.569999999999993</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>10442</v>
       </c>
@@ -5503,7 +8567,7 @@
         <v>67.709999999999994</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>10447</v>
       </c>
@@ -5523,7 +8587,7 @@
         <v>13.19</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>10447</v>
       </c>
@@ -5543,7 +8607,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>10447</v>
       </c>
@@ -5569,7 +8633,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>10447</v>
       </c>
@@ -5595,7 +8659,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>10447</v>
       </c>
@@ -5621,7 +8685,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>10447</v>
       </c>
@@ -5647,7 +8711,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>10447</v>
       </c>
@@ -5673,7 +8737,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>10447</v>
       </c>
@@ -5699,7 +8763,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>10447</v>
       </c>
@@ -5725,7 +8789,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>10447</v>
       </c>
@@ -5751,7 +8815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>10447</v>
       </c>
@@ -5774,7 +8838,7 @@
         <v>66.010000000000005</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>10447</v>
       </c>
@@ -5797,7 +8861,7 @@
         <v>68.349999999999994</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>10452</v>
       </c>
@@ -5817,7 +8881,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>10452</v>
       </c>
@@ -5837,7 +8901,7 @@
         <v>12.97</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>10452</v>
       </c>
@@ -5863,7 +8927,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>10452</v>
       </c>
@@ -5889,7 +8953,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>10452</v>
       </c>
@@ -5915,7 +8979,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>10452</v>
       </c>
@@ -5941,7 +9005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>10452</v>
       </c>
@@ -5967,7 +9031,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>10452</v>
       </c>
@@ -5993,7 +9057,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>10452</v>
       </c>
@@ -6019,7 +9083,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>10452</v>
       </c>
@@ -6045,7 +9109,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>10452</v>
       </c>
@@ -6068,7 +9132,7 @@
         <v>86.86</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>10452</v>
       </c>
@@ -6091,7 +9155,7 @@
         <v>73.61</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>10450</v>
       </c>
@@ -6111,7 +9175,7 @@
         <v>12.86</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>10450</v>
       </c>
@@ -6131,7 +9195,7 @@
         <v>13.01</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>10450</v>
       </c>
@@ -6157,7 +9221,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>10450</v>
       </c>
@@ -6183,7 +9247,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>10450</v>
       </c>
@@ -6209,7 +9273,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>10450</v>
       </c>
@@ -6235,7 +9299,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>10450</v>
       </c>
@@ -6261,7 +9325,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>10450</v>
       </c>
@@ -6287,7 +9351,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>10450</v>
       </c>
@@ -6313,7 +9377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>10450</v>
       </c>
@@ -6339,7 +9403,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>10450</v>
       </c>
@@ -6362,7 +9426,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>10450</v>
       </c>
@@ -6385,7 +9449,7 @@
         <v>67.33</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>10441</v>
       </c>
@@ -6405,7 +9469,7 @@
         <v>12.81</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>10441</v>
       </c>
@@ -6425,7 +9489,7 @@
         <v>13.16</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>10441</v>
       </c>
@@ -6451,7 +9515,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>10441</v>
       </c>
@@ -6477,7 +9541,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>10441</v>
       </c>
@@ -6503,7 +9567,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>10441</v>
       </c>
@@ -6529,7 +9593,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>10441</v>
       </c>
@@ -6555,7 +9619,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>10441</v>
       </c>
@@ -6581,7 +9645,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>10441</v>
       </c>
@@ -6607,7 +9671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>10441</v>
       </c>
@@ -6633,7 +9697,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>10441</v>
       </c>
@@ -6656,7 +9720,7 @@
         <v>67.84</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>10441</v>
       </c>
@@ -6679,7 +9743,7 @@
         <v>70.11</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>10444</v>
       </c>
@@ -6699,7 +9763,7 @@
         <v>13.01</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>10444</v>
       </c>
@@ -6719,7 +9783,7 @@
         <v>12.92</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>10444</v>
       </c>
@@ -6745,7 +9809,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>10444</v>
       </c>
@@ -6771,7 +9835,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>10444</v>
       </c>
@@ -6797,7 +9861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>10444</v>
       </c>
@@ -6823,7 +9887,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>10444</v>
       </c>
@@ -6849,7 +9913,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>10444</v>
       </c>
@@ -6875,7 +9939,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>10444</v>
       </c>
@@ -6901,7 +9965,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>10444</v>
       </c>
@@ -6927,7 +9991,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>10451</v>
       </c>
@@ -6947,7 +10011,7 @@
         <v>12.74</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>10451</v>
       </c>
@@ -6967,7 +10031,7 @@
         <v>13.03</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>10451</v>
       </c>
@@ -6993,7 +10057,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>10451</v>
       </c>
@@ -7019,7 +10083,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>10451</v>
       </c>
@@ -7045,7 +10109,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>10451</v>
       </c>
@@ -7071,7 +10135,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>10451</v>
       </c>
@@ -7097,7 +10161,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>10451</v>
       </c>
@@ -7123,7 +10187,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>10451</v>
       </c>
@@ -7149,7 +10213,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>10451</v>
       </c>
@@ -7175,7 +10239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>10451</v>
       </c>
@@ -7198,7 +10262,7 @@
         <v>65.81</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>10458</v>
       </c>
@@ -7218,7 +10282,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>10458</v>
       </c>
@@ -7238,7 +10302,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>10458</v>
       </c>
@@ -7264,7 +10328,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>10458</v>
       </c>
@@ -7290,7 +10354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>10458</v>
       </c>
@@ -7316,7 +10380,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>10458</v>
       </c>
@@ -7342,7 +10406,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>10458</v>
       </c>
@@ -7368,7 +10432,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>10458</v>
       </c>
@@ -7394,7 +10458,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>10458</v>
       </c>
@@ -7420,7 +10484,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>10458</v>
       </c>
@@ -7446,7 +10510,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>10458</v>
       </c>
@@ -7469,7 +10533,7 @@
         <v>67.709999999999994</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>10458</v>
       </c>
@@ -7492,7 +10556,7 @@
         <v>65.489999999999995</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>10445</v>
       </c>
@@ -7512,7 +10576,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>10445</v>
       </c>
@@ -7532,7 +10596,7 @@
         <v>13.02</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>10445</v>
       </c>
@@ -7558,7 +10622,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>10445</v>
       </c>
@@ -7584,7 +10648,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>10445</v>
       </c>
@@ -7610,7 +10674,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>10445</v>
       </c>
@@ -7636,7 +10700,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>10445</v>
       </c>
@@ -7662,7 +10726,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>10445</v>
       </c>
@@ -7688,7 +10752,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>10445</v>
       </c>
@@ -7714,7 +10778,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>10445</v>
       </c>
@@ -7740,7 +10804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>10445</v>
       </c>
@@ -7763,7 +10827,7 @@
         <v>63.39</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>10445</v>
       </c>
@@ -7786,10 +10850,6 @@
         <v>62.93</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="14" x14ac:dyDescent="0.3"/>
-    <row r="214" spans="1:11" ht="14" x14ac:dyDescent="0.3"/>
-    <row r="215" spans="1:11" ht="14" x14ac:dyDescent="0.3"/>
-    <row r="217" spans="1:11" ht="14" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
